--- a/payload/app/Folder_Data.xlsx
+++ b/payload/app/Folder_Data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\Ingevia\INGEVIA-Email-Assistance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\katay\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B05F8203-898B-4EC6-9B2A-0F95ED0E4F6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7673B1DE-8251-41C4-BCA0-F89D8AAEB50E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{5C19705A-42F0-46F8-960D-DF73BA04C5E9}"/>
   </bookViews>
@@ -24,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -33,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="841" uniqueCount="570">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="697">
   <si>
     <t>ID proyecto</t>
   </si>
@@ -1747,13 +1745,394 @@
   </si>
   <si>
     <t>El proyecto titulado "Accesos hormigonados", registrado bajo el nombre del cliente Francisco Javier Zano con fecha del 18 de diciembre de 2025 y localizado en el municipio alicantino de La Nucía, consiste en el diseño, planificación y ejecución de obras de pavimentación y acondicionamiento de viales o entradas de acceso mediante la utilización de hormigón. Esta intervención está orientada a mejorar la infraestructura de tránsito vehicular o peatonal de la propiedad o zona asignada, garantizando una superficie duradera, resistente al desgaste y adaptada a las condiciones del terreno para optimizar la accesibilidad y la estabilidad de los accesos principales.</t>
+  </si>
+  <si>
+    <t>us298</t>
+  </si>
+  <si>
+    <t>24-004</t>
+  </si>
+  <si>
+    <t>do plenoil</t>
+  </si>
+  <si>
+    <t>us 239</t>
+  </si>
+  <si>
+    <t>us 376</t>
+  </si>
+  <si>
+    <t>us 307</t>
+  </si>
+  <si>
+    <t>us 329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">us 302 </t>
+  </si>
+  <si>
+    <t>us 348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">us 336 </t>
+  </si>
+  <si>
+    <t>24-003</t>
+  </si>
+  <si>
+    <t>us 303A</t>
+  </si>
+  <si>
+    <t>us466</t>
+  </si>
+  <si>
+    <t>us463</t>
+  </si>
+  <si>
+    <t>US423</t>
+  </si>
+  <si>
+    <t>US 433</t>
+  </si>
+  <si>
+    <t>US 460</t>
+  </si>
+  <si>
+    <t>US 459</t>
+  </si>
+  <si>
+    <t>US 458</t>
+  </si>
+  <si>
+    <t>US 455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US402 </t>
+  </si>
+  <si>
+    <t>US 98</t>
+  </si>
+  <si>
+    <t>US063A</t>
+  </si>
+  <si>
+    <t>US084</t>
+  </si>
+  <si>
+    <t>US378</t>
+  </si>
+  <si>
+    <t>US 307 ASK :::::</t>
+  </si>
+  <si>
+    <t>US32A</t>
+  </si>
+  <si>
+    <t>US363</t>
+  </si>
+  <si>
+    <t>US364</t>
+  </si>
+  <si>
+    <t>US351</t>
+  </si>
+  <si>
+    <t>US335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US 310 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">DO PLENOIL </t>
+  </si>
+  <si>
+    <t xml:space="preserve">US 404 </t>
+  </si>
+  <si>
+    <t>US 414</t>
+  </si>
+  <si>
+    <t>US 68B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US 68A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">US 63A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">US 197 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">US 195 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">US 236 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">US 244 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">US 223 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">US 32A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">US316 </t>
+  </si>
+  <si>
+    <t>US0236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US 10 </t>
+  </si>
+  <si>
+    <t>US 162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">US 165 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">US264 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">US264A </t>
+  </si>
+  <si>
+    <t xml:space="preserve">US232 </t>
+  </si>
+  <si>
+    <t>US204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLENOIL </t>
+  </si>
+  <si>
+    <t>24-003-11</t>
+  </si>
+  <si>
+    <t>24-003-12</t>
+  </si>
+  <si>
+    <t>24-004-13</t>
+  </si>
+  <si>
+    <t>24-004-14</t>
+  </si>
+  <si>
+    <t>24-004-15</t>
+  </si>
+  <si>
+    <t>24-004-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-004-03 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-004-06 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-004-11 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">24-004-12 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23-004-05 </t>
+  </si>
+  <si>
+    <t>23-004-12</t>
+  </si>
+  <si>
+    <t>23-003-11</t>
+  </si>
+  <si>
+    <t>23-004-01</t>
+  </si>
+  <si>
+    <t>23-004-03</t>
+  </si>
+  <si>
+    <t>23-004-06</t>
+  </si>
+  <si>
+    <t>23-004-08</t>
+  </si>
+  <si>
+    <t>23-004-10</t>
+  </si>
+  <si>
+    <t>23-003-19</t>
+  </si>
+  <si>
+    <t>23-004-13</t>
+  </si>
+  <si>
+    <t>23-003-05</t>
+  </si>
+  <si>
+    <t>23-004</t>
+  </si>
+  <si>
+    <t>22-004</t>
+  </si>
+  <si>
+    <t>22-003</t>
+  </si>
+  <si>
+    <t>21-003</t>
+  </si>
+  <si>
+    <t>21-005</t>
+  </si>
+  <si>
+    <t>21-004</t>
+  </si>
+  <si>
+    <t>Plenoil</t>
+  </si>
+  <si>
+    <t>DO Plenoil</t>
+  </si>
+  <si>
+    <t>DO AV ENRIQUE GIMENO 48 CASTELLON</t>
+  </si>
+  <si>
+    <t>DO SERRA CORBERA SAGUNTO</t>
+  </si>
+  <si>
+    <t>DO PLA DEL VIVER 4-6 VILAFRANCA I DEL PENEDES (US307)</t>
+  </si>
+  <si>
+    <t>DO LA CRUZ 1 PUZOL</t>
+  </si>
+  <si>
+    <t>DO AV CASTELL VELL 40 CASTELLON</t>
+  </si>
+  <si>
+    <t>DO AV_EUROPA 1 VILLAREAL</t>
+  </si>
+  <si>
+    <t>CTRA DE VALENCIA Km 8,8 CUARTE DE HUERVA ZARAGOZA</t>
+  </si>
+  <si>
+    <t>VALENCIA-BARNA 60 VINAROZ</t>
+  </si>
+  <si>
+    <t>CL SECTOR 1 ALFAFAR</t>
+  </si>
+  <si>
+    <t>CTRA DEL PLA 148 VALLS TARRAGONA</t>
+  </si>
+  <si>
+    <t>DO PL NUM 55 ALM SERV 108 CULLERA</t>
+  </si>
+  <si>
+    <t>DO TETUÁN 2 GANDIA</t>
+  </si>
+  <si>
+    <t>DO C NANTES 1 PARLA</t>
+  </si>
+  <si>
+    <t>DO AV PREMIOS NOBEL 1 TORREJON DE ARDOZ</t>
+  </si>
+  <si>
+    <t>DO POLIGONO INDUSTRIAL F PARCELA 18 XÁTIVA</t>
+  </si>
+  <si>
+    <t>DO CTRA DEL MIG 36 HOSPITALET</t>
+  </si>
+  <si>
+    <t>DO LAVADERO PTO SAGUNTO 349</t>
+  </si>
+  <si>
+    <t>DO CAMI VELL GANDIA 32 BELLREGUARD</t>
+  </si>
+  <si>
+    <t>DO SECTOR PI-PN1, N-301 MURCIA I (US084)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> VITAL 12 GANDÍA</t>
+  </si>
+  <si>
+    <t>PLA DEL VIVER 4-6 VILAFRANCA DEL PENEDES</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DO MARCHAL MASSALFASSAR</t>
+  </si>
+  <si>
+    <t>DO AVDA GUADASSUAR 4 EL SERRALLO ALCUDIA</t>
+  </si>
+  <si>
+    <t>DO C_OLIVA 4 DAIMUZ</t>
+  </si>
+  <si>
+    <t>DO VALENCIA-BARNA 37 VINAROZ</t>
+  </si>
+  <si>
+    <t>DO AV BENICASIM 24 CASTELLON</t>
+  </si>
+  <si>
+    <t>PL NUM 55 ALM SERV 108 CULLERA</t>
+  </si>
+  <si>
+    <t>DO CMNO MONCADA 127 VALENCIA</t>
+  </si>
+  <si>
+    <t>DO CAMI LLOMA 2 ALDAIA</t>
+  </si>
+  <si>
+    <t>DO MARCHAL MASSALFASSAR</t>
+  </si>
+  <si>
+    <t>DO ROSAS 13 QUART DE POBLET</t>
+  </si>
+  <si>
+    <t>DO MORAIRA - TEULADA I</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> DO TORREVIEJA IV LAS BARCAS</t>
+  </si>
+  <si>
+    <t>DO ACEQUIA MANEGA 8 MASSANASSA</t>
+  </si>
+  <si>
+    <t>DO LLUCENA 12 ONDA</t>
+  </si>
+  <si>
+    <t>MARCHAL MASSALFASSAR</t>
+  </si>
+  <si>
+    <t>LAS BARCAS TORREVIEJA</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LAVADERO LA NUCIA</t>
+  </si>
+  <si>
+    <t>DO VISTAHERMOSA II CARRATALÁ</t>
+  </si>
+  <si>
+    <t>DO SANTA ALODIA ORIHUELA COSTA</t>
+  </si>
+  <si>
+    <t>AVDA RAJOLAR 4 CHIRIVELLA</t>
+  </si>
+  <si>
+    <t>DO AVDA RAJOLAR 4 CHIRIVELLA</t>
+  </si>
+  <si>
+    <t>DO TORREVIEJA LORCA GARCÍA</t>
+  </si>
+  <si>
+    <t>DO ALVARIÑO ALBIR (ALFAZ DEL PI)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -1786,6 +2165,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -1795,7 +2180,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1890,11 +2275,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right style="thin">
+        <color indexed="11"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="11"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1949,6 +2354,27 @@
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3109,7 +3535,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB39E78E-1493-41EB-B910-686E4C0243D7}">
-  <dimension ref="A1:G170"/>
+  <dimension ref="A1:G220"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -3121,7 +3547,7 @@
     <col min="8" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.65" customHeight="1">
+    <row r="1" spans="1:7" ht="14.75" customHeight="1">
       <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
@@ -3142,7 +3568,7 @@
       </c>
       <c r="G1" s="3"/>
     </row>
-    <row r="2" spans="1:7" ht="14.65" customHeight="1">
+    <row r="2" spans="1:7" ht="14.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
@@ -3163,7 +3589,7 @@
       </c>
       <c r="G2" s="3"/>
     </row>
-    <row r="3" spans="1:7" ht="14.65" customHeight="1">
+    <row r="3" spans="1:7" ht="14.75" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>9</v>
       </c>
@@ -3184,7 +3610,7 @@
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" ht="14.65" customHeight="1">
+    <row r="4" spans="1:7" ht="14.75" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>12</v>
       </c>
@@ -3205,7 +3631,7 @@
       </c>
       <c r="G4" s="3"/>
     </row>
-    <row r="5" spans="1:7" ht="14.65" customHeight="1">
+    <row r="5" spans="1:7" ht="14.75" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>14</v>
       </c>
@@ -3226,7 +3652,7 @@
       </c>
       <c r="G5" s="3"/>
     </row>
-    <row r="6" spans="1:7" ht="14.65" customHeight="1">
+    <row r="6" spans="1:7" ht="14.75" customHeight="1">
       <c r="A6" s="8" t="s">
         <v>16</v>
       </c>
@@ -3247,7 +3673,7 @@
       </c>
       <c r="G6" s="3"/>
     </row>
-    <row r="7" spans="1:7" ht="14.65" customHeight="1">
+    <row r="7" spans="1:7" ht="14.75" customHeight="1">
       <c r="A7" s="8" t="s">
         <v>16</v>
       </c>
@@ -3268,7 +3694,7 @@
       </c>
       <c r="G7" s="3"/>
     </row>
-    <row r="8" spans="1:7" ht="14.65" customHeight="1">
+    <row r="8" spans="1:7" ht="14.75" customHeight="1">
       <c r="A8" s="8" t="s">
         <v>19</v>
       </c>
@@ -3289,7 +3715,7 @@
       </c>
       <c r="G8" s="3"/>
     </row>
-    <row r="9" spans="1:7" ht="14.65" customHeight="1">
+    <row r="9" spans="1:7" ht="14.75" customHeight="1">
       <c r="A9" s="8" t="s">
         <v>21</v>
       </c>
@@ -3310,7 +3736,7 @@
       </c>
       <c r="G9" s="3"/>
     </row>
-    <row r="10" spans="1:7" ht="14.65" customHeight="1">
+    <row r="10" spans="1:7" ht="14.75" customHeight="1">
       <c r="A10" s="8" t="s">
         <v>23</v>
       </c>
@@ -3331,7 +3757,7 @@
       </c>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:7" ht="14.65" customHeight="1">
+    <row r="11" spans="1:7" ht="14.75" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>26</v>
       </c>
@@ -3352,7 +3778,7 @@
       </c>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7" ht="14.65" customHeight="1">
+    <row r="12" spans="1:7" ht="14.75" customHeight="1">
       <c r="A12" s="8" t="s">
         <v>28</v>
       </c>
@@ -3373,7 +3799,7 @@
       </c>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:7" ht="14.65" customHeight="1">
+    <row r="13" spans="1:7" ht="14.75" customHeight="1">
       <c r="A13" s="8" t="s">
         <v>30</v>
       </c>
@@ -3394,7 +3820,7 @@
       </c>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:7" ht="14.65" customHeight="1">
+    <row r="14" spans="1:7" ht="14.75" customHeight="1">
       <c r="A14" s="8" t="s">
         <v>32</v>
       </c>
@@ -3415,7 +3841,7 @@
       </c>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" ht="14.65" customHeight="1">
+    <row r="15" spans="1:7" ht="14.75" customHeight="1">
       <c r="A15" s="8" t="s">
         <v>34</v>
       </c>
@@ -3436,7 +3862,7 @@
       </c>
       <c r="G15" s="3"/>
     </row>
-    <row r="16" spans="1:7" ht="14.65" customHeight="1">
+    <row r="16" spans="1:7" ht="14.75" customHeight="1">
       <c r="A16" s="8" t="s">
         <v>36</v>
       </c>
@@ -3457,7 +3883,7 @@
       </c>
       <c r="G16" s="3"/>
     </row>
-    <row r="17" spans="1:7" ht="14.65" customHeight="1">
+    <row r="17" spans="1:7" ht="14.75" customHeight="1">
       <c r="A17" s="8" t="s">
         <v>38</v>
       </c>
@@ -3478,7 +3904,7 @@
       </c>
       <c r="G17" s="3"/>
     </row>
-    <row r="18" spans="1:7" ht="14.65" customHeight="1">
+    <row r="18" spans="1:7" ht="14.75" customHeight="1">
       <c r="A18" s="8" t="s">
         <v>40</v>
       </c>
@@ -3499,7 +3925,7 @@
       </c>
       <c r="G18" s="3"/>
     </row>
-    <row r="19" spans="1:7" ht="14.65" customHeight="1">
+    <row r="19" spans="1:7" ht="14.75" customHeight="1">
       <c r="A19" s="8" t="s">
         <v>42</v>
       </c>
@@ -3522,7 +3948,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="14.65" customHeight="1">
+    <row r="20" spans="1:7" ht="14.75" customHeight="1">
       <c r="A20" s="8" t="s">
         <v>45</v>
       </c>
@@ -3543,7 +3969,7 @@
       </c>
       <c r="G20" s="3"/>
     </row>
-    <row r="21" spans="1:7" ht="14.65" customHeight="1">
+    <row r="21" spans="1:7" ht="14.75" customHeight="1">
       <c r="A21" s="8" t="s">
         <v>47</v>
       </c>
@@ -3564,7 +3990,7 @@
       </c>
       <c r="G21" s="3"/>
     </row>
-    <row r="22" spans="1:7" ht="14.65" customHeight="1">
+    <row r="22" spans="1:7" ht="14.75" customHeight="1">
       <c r="A22" s="8" t="s">
         <v>49</v>
       </c>
@@ -3585,7 +4011,7 @@
       </c>
       <c r="G22" s="3"/>
     </row>
-    <row r="23" spans="1:7" ht="14.65" customHeight="1">
+    <row r="23" spans="1:7" ht="14.75" customHeight="1">
       <c r="A23" s="8" t="s">
         <v>51</v>
       </c>
@@ -3606,7 +4032,7 @@
       </c>
       <c r="G23" s="3"/>
     </row>
-    <row r="24" spans="1:7" ht="14.65" customHeight="1">
+    <row r="24" spans="1:7" ht="14.75" customHeight="1">
       <c r="A24" s="8" t="s">
         <v>52</v>
       </c>
@@ -3627,7 +4053,7 @@
       </c>
       <c r="G24" s="3"/>
     </row>
-    <row r="25" spans="1:7" ht="14.65" customHeight="1">
+    <row r="25" spans="1:7" ht="14.75" customHeight="1">
       <c r="A25" s="8" t="s">
         <v>54</v>
       </c>
@@ -3648,7 +4074,7 @@
       </c>
       <c r="G25" s="3"/>
     </row>
-    <row r="26" spans="1:7" ht="14.65" customHeight="1">
+    <row r="26" spans="1:7" ht="14.75" customHeight="1">
       <c r="A26" s="8" t="s">
         <v>56</v>
       </c>
@@ -3669,7 +4095,7 @@
       </c>
       <c r="G26" s="3"/>
     </row>
-    <row r="27" spans="1:7" ht="14.65" customHeight="1">
+    <row r="27" spans="1:7" ht="14.75" customHeight="1">
       <c r="A27" s="8" t="s">
         <v>58</v>
       </c>
@@ -3690,7 +4116,7 @@
       </c>
       <c r="G27" s="3"/>
     </row>
-    <row r="28" spans="1:7" ht="14.65" customHeight="1">
+    <row r="28" spans="1:7" ht="14.75" customHeight="1">
       <c r="A28" s="8" t="s">
         <v>60</v>
       </c>
@@ -3711,7 +4137,7 @@
       </c>
       <c r="G28" s="3"/>
     </row>
-    <row r="29" spans="1:7" ht="14.65" customHeight="1">
+    <row r="29" spans="1:7" ht="14.75" customHeight="1">
       <c r="A29" s="8" t="s">
         <v>61</v>
       </c>
@@ -3732,7 +4158,7 @@
       </c>
       <c r="G29" s="3"/>
     </row>
-    <row r="30" spans="1:7" ht="14.65" customHeight="1">
+    <row r="30" spans="1:7" ht="14.75" customHeight="1">
       <c r="A30" s="8" t="s">
         <v>64</v>
       </c>
@@ -3753,7 +4179,7 @@
       </c>
       <c r="G30" s="3"/>
     </row>
-    <row r="31" spans="1:7" ht="14.65" customHeight="1">
+    <row r="31" spans="1:7" ht="14.75" customHeight="1">
       <c r="A31" s="8" t="s">
         <v>64</v>
       </c>
@@ -3774,7 +4200,7 @@
       </c>
       <c r="G31" s="3"/>
     </row>
-    <row r="32" spans="1:7" ht="14.65" customHeight="1">
+    <row r="32" spans="1:7" ht="14.75" customHeight="1">
       <c r="A32" s="8" t="s">
         <v>64</v>
       </c>
@@ -3795,7 +4221,7 @@
       </c>
       <c r="G32" s="3"/>
     </row>
-    <row r="33" spans="1:7" ht="14.65" customHeight="1">
+    <row r="33" spans="1:7" ht="14.75" customHeight="1">
       <c r="A33" s="8" t="s">
         <v>64</v>
       </c>
@@ -3816,7 +4242,7 @@
       </c>
       <c r="G33" s="3"/>
     </row>
-    <row r="34" spans="1:7" ht="14.65" customHeight="1">
+    <row r="34" spans="1:7" ht="14.75" customHeight="1">
       <c r="A34" s="8" t="s">
         <v>64</v>
       </c>
@@ -3837,7 +4263,7 @@
       </c>
       <c r="G34" s="3"/>
     </row>
-    <row r="35" spans="1:7" ht="14.65" customHeight="1">
+    <row r="35" spans="1:7" ht="14.75" customHeight="1">
       <c r="A35" s="8" t="s">
         <v>64</v>
       </c>
@@ -3858,7 +4284,7 @@
       </c>
       <c r="G35" s="3"/>
     </row>
-    <row r="36" spans="1:7" ht="14.65" customHeight="1">
+    <row r="36" spans="1:7" ht="14.75" customHeight="1">
       <c r="A36" s="8" t="s">
         <v>64</v>
       </c>
@@ -3879,7 +4305,7 @@
       </c>
       <c r="G36" s="3"/>
     </row>
-    <row r="37" spans="1:7" ht="14.65" customHeight="1">
+    <row r="37" spans="1:7" ht="14.75" customHeight="1">
       <c r="A37" s="8" t="s">
         <v>66</v>
       </c>
@@ -3900,7 +4326,7 @@
       </c>
       <c r="G37" s="3"/>
     </row>
-    <row r="38" spans="1:7" ht="14.65" customHeight="1">
+    <row r="38" spans="1:7" ht="14.75" customHeight="1">
       <c r="A38" s="8" t="s">
         <v>69</v>
       </c>
@@ -3921,7 +4347,7 @@
       </c>
       <c r="G38" s="3"/>
     </row>
-    <row r="39" spans="1:7" ht="14.65" customHeight="1">
+    <row r="39" spans="1:7" ht="14.75" customHeight="1">
       <c r="A39" s="8" t="s">
         <v>72</v>
       </c>
@@ -3942,7 +4368,7 @@
       </c>
       <c r="G39" s="3"/>
     </row>
-    <row r="40" spans="1:7" ht="14.65" customHeight="1">
+    <row r="40" spans="1:7" ht="14.75" customHeight="1">
       <c r="A40" s="8" t="s">
         <v>74</v>
       </c>
@@ -3963,7 +4389,7 @@
       </c>
       <c r="G40" s="3"/>
     </row>
-    <row r="41" spans="1:7" ht="14.65" customHeight="1">
+    <row r="41" spans="1:7" ht="14.75" customHeight="1">
       <c r="A41" s="8" t="s">
         <v>76</v>
       </c>
@@ -3984,7 +4410,7 @@
       </c>
       <c r="G41" s="3"/>
     </row>
-    <row r="42" spans="1:7" ht="14.65" customHeight="1">
+    <row r="42" spans="1:7" ht="14.75" customHeight="1">
       <c r="A42" s="8" t="s">
         <v>79</v>
       </c>
@@ -4005,7 +4431,7 @@
       </c>
       <c r="G42" s="3"/>
     </row>
-    <row r="43" spans="1:7" ht="14.65" customHeight="1">
+    <row r="43" spans="1:7" ht="14.75" customHeight="1">
       <c r="A43" s="8" t="s">
         <v>82</v>
       </c>
@@ -4026,7 +4452,7 @@
       </c>
       <c r="G43" s="3"/>
     </row>
-    <row r="44" spans="1:7" ht="14.65" customHeight="1">
+    <row r="44" spans="1:7" ht="14.75" customHeight="1">
       <c r="A44" s="8" t="s">
         <v>85</v>
       </c>
@@ -4047,7 +4473,7 @@
       </c>
       <c r="G44" s="3"/>
     </row>
-    <row r="45" spans="1:7" ht="14.65" customHeight="1">
+    <row r="45" spans="1:7" ht="14.75" customHeight="1">
       <c r="A45" s="8" t="s">
         <v>87</v>
       </c>
@@ -4068,7 +4494,7 @@
       </c>
       <c r="G45" s="3"/>
     </row>
-    <row r="46" spans="1:7" ht="14.65" customHeight="1">
+    <row r="46" spans="1:7" ht="14.75" customHeight="1">
       <c r="A46" s="8" t="s">
         <v>89</v>
       </c>
@@ -4089,7 +4515,7 @@
       </c>
       <c r="G46" s="3"/>
     </row>
-    <row r="47" spans="1:7" ht="14.65" customHeight="1">
+    <row r="47" spans="1:7" ht="14.75" customHeight="1">
       <c r="A47" s="8" t="s">
         <v>92</v>
       </c>
@@ -4110,7 +4536,7 @@
       </c>
       <c r="G47" s="3"/>
     </row>
-    <row r="48" spans="1:7" ht="14.65" customHeight="1">
+    <row r="48" spans="1:7" ht="14.75" customHeight="1">
       <c r="A48" s="8" t="s">
         <v>95</v>
       </c>
@@ -4131,7 +4557,7 @@
       </c>
       <c r="G48" s="3"/>
     </row>
-    <row r="49" spans="1:7" ht="14.65" customHeight="1">
+    <row r="49" spans="1:7" ht="14.75" customHeight="1">
       <c r="A49" s="8" t="s">
         <v>98</v>
       </c>
@@ -4152,7 +4578,7 @@
       </c>
       <c r="G49" s="3"/>
     </row>
-    <row r="50" spans="1:7" ht="14.65" customHeight="1">
+    <row r="50" spans="1:7" ht="14.75" customHeight="1">
       <c r="A50" s="8" t="s">
         <v>101</v>
       </c>
@@ -4173,7 +4599,7 @@
       </c>
       <c r="G50" s="3"/>
     </row>
-    <row r="51" spans="1:7" ht="14.65" customHeight="1">
+    <row r="51" spans="1:7" ht="14.75" customHeight="1">
       <c r="A51" s="8" t="s">
         <v>104</v>
       </c>
@@ -4194,7 +4620,7 @@
       </c>
       <c r="G51" s="3"/>
     </row>
-    <row r="52" spans="1:7" ht="14.65" customHeight="1">
+    <row r="52" spans="1:7" ht="14.75" customHeight="1">
       <c r="A52" s="8" t="s">
         <v>107</v>
       </c>
@@ -4215,7 +4641,7 @@
       </c>
       <c r="G52" s="3"/>
     </row>
-    <row r="53" spans="1:7" ht="14.65" customHeight="1">
+    <row r="53" spans="1:7" ht="14.75" customHeight="1">
       <c r="A53" s="8" t="s">
         <v>110</v>
       </c>
@@ -4236,7 +4662,7 @@
       </c>
       <c r="G53" s="3"/>
     </row>
-    <row r="54" spans="1:7" ht="14.65" customHeight="1">
+    <row r="54" spans="1:7" ht="14.75" customHeight="1">
       <c r="A54" s="8" t="s">
         <v>113</v>
       </c>
@@ -4257,7 +4683,7 @@
       </c>
       <c r="G54" s="3"/>
     </row>
-    <row r="55" spans="1:7" ht="14.65" customHeight="1">
+    <row r="55" spans="1:7" ht="14.75" customHeight="1">
       <c r="A55" s="8" t="s">
         <v>116</v>
       </c>
@@ -4278,7 +4704,7 @@
       </c>
       <c r="G55" s="3"/>
     </row>
-    <row r="56" spans="1:7" ht="14.65" customHeight="1">
+    <row r="56" spans="1:7" ht="14.75" customHeight="1">
       <c r="A56" s="8" t="s">
         <v>119</v>
       </c>
@@ -4299,7 +4725,7 @@
       </c>
       <c r="G56" s="3"/>
     </row>
-    <row r="57" spans="1:7" ht="14.65" customHeight="1">
+    <row r="57" spans="1:7" ht="14.75" customHeight="1">
       <c r="A57" s="8" t="s">
         <v>122</v>
       </c>
@@ -4320,7 +4746,7 @@
       </c>
       <c r="G57" s="3"/>
     </row>
-    <row r="58" spans="1:7" ht="14.65" customHeight="1">
+    <row r="58" spans="1:7" ht="14.75" customHeight="1">
       <c r="A58" s="8" t="s">
         <v>125</v>
       </c>
@@ -4341,7 +4767,7 @@
       </c>
       <c r="G58" s="3"/>
     </row>
-    <row r="59" spans="1:7" ht="14.65" customHeight="1">
+    <row r="59" spans="1:7" ht="14.75" customHeight="1">
       <c r="A59" s="8" t="s">
         <v>128</v>
       </c>
@@ -6670,6 +7096,1003 @@
         <v>569</v>
       </c>
       <c r="G170" s="3"/>
+    </row>
+    <row r="171" spans="1:7" ht="15" customHeight="1">
+      <c r="A171" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="B171" s="29" t="s">
+        <v>572</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="D171" s="37">
+        <v>2024</v>
+      </c>
+      <c r="E171" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F171" s="28" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" ht="15" customHeight="1">
+      <c r="A172" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="B172" s="29" t="s">
+        <v>572</v>
+      </c>
+      <c r="C172" s="30" t="s">
+        <v>653</v>
+      </c>
+      <c r="D172" s="37">
+        <v>2024</v>
+      </c>
+      <c r="E172" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F172" s="28" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" ht="15" customHeight="1">
+      <c r="A173" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="B173" s="29" t="s">
+        <v>572</v>
+      </c>
+      <c r="C173" s="30" t="s">
+        <v>656</v>
+      </c>
+      <c r="D173" s="37">
+        <v>2024</v>
+      </c>
+      <c r="E173" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F173" s="28" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" ht="15" customHeight="1">
+      <c r="A174" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="B174" s="29" t="s">
+        <v>572</v>
+      </c>
+      <c r="C174" s="36" t="s">
+        <v>655</v>
+      </c>
+      <c r="D174" s="37">
+        <v>2024</v>
+      </c>
+      <c r="E174" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F174" s="28" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" ht="15" customHeight="1">
+      <c r="A175" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="B175" s="29" t="s">
+        <v>572</v>
+      </c>
+      <c r="C175" s="36" t="s">
+        <v>657</v>
+      </c>
+      <c r="D175" s="37">
+        <v>2024</v>
+      </c>
+      <c r="E175" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F175" s="28" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" ht="15" customHeight="1">
+      <c r="A176" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="B176" s="29" t="s">
+        <v>572</v>
+      </c>
+      <c r="C176" s="30" t="s">
+        <v>658</v>
+      </c>
+      <c r="D176" s="37">
+        <v>2024</v>
+      </c>
+      <c r="E176" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F176" s="28" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" ht="15" customHeight="1">
+      <c r="A177" s="29" t="s">
+        <v>571</v>
+      </c>
+      <c r="B177" s="29" t="s">
+        <v>572</v>
+      </c>
+      <c r="C177" s="30" t="s">
+        <v>654</v>
+      </c>
+      <c r="D177" s="37">
+        <v>2024</v>
+      </c>
+      <c r="E177" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F177" s="28" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" ht="15" customHeight="1">
+      <c r="A178" s="29" t="s">
+        <v>580</v>
+      </c>
+      <c r="B178" s="29" t="s">
+        <v>572</v>
+      </c>
+      <c r="C178" s="30" t="s">
+        <v>659</v>
+      </c>
+      <c r="D178" s="37">
+        <v>2024</v>
+      </c>
+      <c r="E178" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="F178" s="28" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" ht="15" customHeight="1">
+      <c r="A179" s="29" t="s">
+        <v>580</v>
+      </c>
+      <c r="B179" s="29" t="s">
+        <v>572</v>
+      </c>
+      <c r="C179" s="30" t="s">
+        <v>660</v>
+      </c>
+      <c r="D179" s="37">
+        <v>2024</v>
+      </c>
+      <c r="E179" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="F179" s="28" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" ht="15" customHeight="1">
+      <c r="A180" s="35" t="s">
+        <v>624</v>
+      </c>
+      <c r="B180" s="33" t="s">
+        <v>623</v>
+      </c>
+      <c r="C180" s="35" t="s">
+        <v>661</v>
+      </c>
+      <c r="D180" s="38">
+        <v>2024</v>
+      </c>
+      <c r="E180" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="F180" s="32" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" ht="15" customHeight="1">
+      <c r="A181" s="35" t="s">
+        <v>625</v>
+      </c>
+      <c r="B181" s="33" t="s">
+        <v>623</v>
+      </c>
+      <c r="C181" s="31" t="s">
+        <v>662</v>
+      </c>
+      <c r="D181" s="38">
+        <v>2024</v>
+      </c>
+      <c r="E181" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="F181" s="32" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" ht="15" customHeight="1">
+      <c r="A182" s="35" t="s">
+        <v>630</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C182" s="35" t="s">
+        <v>663</v>
+      </c>
+      <c r="D182" s="38">
+        <v>2024</v>
+      </c>
+      <c r="E182" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F182" s="32" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" ht="15" customHeight="1">
+      <c r="A183" s="33" t="s">
+        <v>631</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C183" s="31" t="s">
+        <v>664</v>
+      </c>
+      <c r="D183" s="38">
+        <v>2024</v>
+      </c>
+      <c r="E183" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F183" s="32" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" ht="15" customHeight="1">
+      <c r="A184" s="35" t="s">
+        <v>632</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C184" s="31" t="s">
+        <v>665</v>
+      </c>
+      <c r="D184" s="38">
+        <v>2024</v>
+      </c>
+      <c r="E184" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F184" s="32" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" ht="15" customHeight="1">
+      <c r="A185" s="35" t="s">
+        <v>633</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C185" s="31" t="s">
+        <v>666</v>
+      </c>
+      <c r="D185" s="38">
+        <v>2024</v>
+      </c>
+      <c r="E185" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F185" s="32" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" ht="15" customHeight="1">
+      <c r="A186" s="35" t="s">
+        <v>626</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C186" s="31" t="s">
+        <v>667</v>
+      </c>
+      <c r="D186" s="38">
+        <v>2024</v>
+      </c>
+      <c r="E186" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F186" s="32" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" ht="15" customHeight="1">
+      <c r="A187" s="33" t="s">
+        <v>627</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C187" s="31" t="s">
+        <v>668</v>
+      </c>
+      <c r="D187" s="38">
+        <v>2024</v>
+      </c>
+      <c r="E187" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F187" s="32" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" ht="15" customHeight="1">
+      <c r="A188" s="35" t="s">
+        <v>628</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C188" s="31" t="s">
+        <v>653</v>
+      </c>
+      <c r="D188" s="38">
+        <v>2024</v>
+      </c>
+      <c r="E188" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F188" s="32" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" ht="15" customHeight="1">
+      <c r="A189" s="35" t="s">
+        <v>629</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C189" s="31" t="s">
+        <v>669</v>
+      </c>
+      <c r="D189" s="38">
+        <v>2024</v>
+      </c>
+      <c r="E189" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F189" s="32" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" ht="15" customHeight="1">
+      <c r="A190" s="35" t="s">
+        <v>634</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C190" s="35" t="s">
+        <v>670</v>
+      </c>
+      <c r="D190" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E190" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F190" s="34" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" ht="15" customHeight="1">
+      <c r="A191" s="33" t="s">
+        <v>635</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C191" s="31" t="s">
+        <v>671</v>
+      </c>
+      <c r="D191" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E191" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F191" s="34" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" ht="15" customHeight="1">
+      <c r="A192" s="33" t="s">
+        <v>644</v>
+      </c>
+      <c r="B192" s="33" t="s">
+        <v>623</v>
+      </c>
+      <c r="C192" s="31" t="s">
+        <v>672</v>
+      </c>
+      <c r="D192" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E192" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="F192" s="32" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" ht="15" customHeight="1">
+      <c r="A193" s="33" t="s">
+        <v>636</v>
+      </c>
+      <c r="B193" s="33" t="s">
+        <v>623</v>
+      </c>
+      <c r="C193" s="35" t="s">
+        <v>673</v>
+      </c>
+      <c r="D193" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E193" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="F193" s="34" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" ht="15" customHeight="1">
+      <c r="A194" s="33" t="s">
+        <v>637</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C194" s="35" t="s">
+        <v>674</v>
+      </c>
+      <c r="D194" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E194" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F194" s="32" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" ht="15" customHeight="1">
+      <c r="A195" s="33" t="s">
+        <v>638</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C195" s="35" t="s">
+        <v>675</v>
+      </c>
+      <c r="D195" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E195" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F195" s="32" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" ht="15" customHeight="1">
+      <c r="B196" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C196" s="35" t="s">
+        <v>675</v>
+      </c>
+      <c r="D196" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E196" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F196" s="32" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" ht="15" customHeight="1">
+      <c r="A197" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C197" s="31" t="s">
+        <v>676</v>
+      </c>
+      <c r="D197" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E197" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F197" s="32" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" ht="15" customHeight="1">
+      <c r="A198" s="33" t="s">
+        <v>640</v>
+      </c>
+      <c r="B198" s="33" t="s">
+        <v>602</v>
+      </c>
+      <c r="C198" s="31" t="s">
+        <v>677</v>
+      </c>
+      <c r="D198" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E198" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F198" s="32" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" ht="15" customHeight="1">
+      <c r="A199" s="33" t="s">
+        <v>641</v>
+      </c>
+      <c r="B199" s="33" t="s">
+        <v>602</v>
+      </c>
+      <c r="C199" s="31" t="s">
+        <v>678</v>
+      </c>
+      <c r="D199" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E199" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F199" s="34" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" ht="15" customHeight="1">
+      <c r="A200" s="33" t="s">
+        <v>642</v>
+      </c>
+      <c r="B200" s="33" t="s">
+        <v>623</v>
+      </c>
+      <c r="C200" s="35" t="s">
+        <v>679</v>
+      </c>
+      <c r="D200" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E200" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="F200" s="34" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" ht="15" customHeight="1">
+      <c r="A201" s="33" t="s">
+        <v>643</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C201" s="35" t="s">
+        <v>680</v>
+      </c>
+      <c r="D201" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E201" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F201" s="34" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" ht="15" customHeight="1">
+      <c r="A202" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C202" s="35" t="s">
+        <v>681</v>
+      </c>
+      <c r="D202" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E202" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F202" s="34" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" ht="15" customHeight="1">
+      <c r="A203" s="33" t="s">
+        <v>645</v>
+      </c>
+      <c r="B203" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C203" s="35" t="s">
+        <v>682</v>
+      </c>
+      <c r="D203" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E203" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F203" s="34" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" ht="15" customHeight="1">
+      <c r="A204" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B204" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C204" s="35" t="s">
+        <v>683</v>
+      </c>
+      <c r="D204" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E204" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F204" s="34" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" ht="15" customHeight="1">
+      <c r="A205" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="B205" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C205" s="35" t="s">
+        <v>670</v>
+      </c>
+      <c r="D205" s="38">
+        <v>2023</v>
+      </c>
+      <c r="E205" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F205" s="34" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" ht="15" customHeight="1">
+      <c r="A206" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B206" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C206" s="35" t="s">
+        <v>684</v>
+      </c>
+      <c r="D206" s="38">
+        <v>2022</v>
+      </c>
+      <c r="E206" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F206" s="34" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" ht="15" customHeight="1">
+      <c r="A207" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B207" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C207" s="35" t="s">
+        <v>684</v>
+      </c>
+      <c r="D207" s="38">
+        <v>2022</v>
+      </c>
+      <c r="E207" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F207" s="34" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" ht="15" customHeight="1">
+      <c r="A208" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B208" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C208" s="35" t="s">
+        <v>685</v>
+      </c>
+      <c r="D208" s="38">
+        <v>2022</v>
+      </c>
+      <c r="E208" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F208" s="34" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" ht="15" customHeight="1">
+      <c r="A209" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B209" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C209" s="35" t="s">
+        <v>686</v>
+      </c>
+      <c r="D209" s="38">
+        <v>2022</v>
+      </c>
+      <c r="E209" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F209" s="34" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" ht="15" customHeight="1">
+      <c r="A210" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B210" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C210" s="35" t="s">
+        <v>687</v>
+      </c>
+      <c r="D210" s="38">
+        <v>2022</v>
+      </c>
+      <c r="E210" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F210" s="34" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" ht="15" customHeight="1">
+      <c r="A211" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="B211" s="1" t="s">
+        <v>623</v>
+      </c>
+      <c r="C211" s="35" t="s">
+        <v>688</v>
+      </c>
+      <c r="D211" s="38">
+        <v>2022</v>
+      </c>
+      <c r="E211" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="F211" s="34" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" ht="15" customHeight="1">
+      <c r="A212" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="B212" s="33" t="s">
+        <v>602</v>
+      </c>
+      <c r="C212" s="35" t="s">
+        <v>687</v>
+      </c>
+      <c r="D212" s="38">
+        <v>2022</v>
+      </c>
+      <c r="E212" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F212" s="34" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" ht="15" customHeight="1">
+      <c r="A213" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B213" s="33" t="s">
+        <v>623</v>
+      </c>
+      <c r="C213" s="35" t="s">
+        <v>689</v>
+      </c>
+      <c r="D213" s="38">
+        <v>2021</v>
+      </c>
+      <c r="E213" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="F213" s="34" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" ht="15" customHeight="1">
+      <c r="A214" s="33" t="s">
+        <v>648</v>
+      </c>
+      <c r="B214" s="33" t="s">
+        <v>623</v>
+      </c>
+      <c r="C214" s="35" t="s">
+        <v>690</v>
+      </c>
+      <c r="D214" s="38">
+        <v>2021</v>
+      </c>
+      <c r="E214" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="F214" s="34" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" ht="15" customHeight="1">
+      <c r="A215" s="33" t="s">
+        <v>650</v>
+      </c>
+      <c r="B215" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C215" s="35" t="s">
+        <v>691</v>
+      </c>
+      <c r="D215" s="38">
+        <v>2021</v>
+      </c>
+      <c r="E215" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F215" s="34" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" ht="15" customHeight="1">
+      <c r="A216" s="33" t="s">
+        <v>650</v>
+      </c>
+      <c r="B216" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C216" s="35" t="s">
+        <v>692</v>
+      </c>
+      <c r="D216" s="38">
+        <v>2021</v>
+      </c>
+      <c r="E216" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F216" s="34" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" ht="15" customHeight="1">
+      <c r="A217" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="B217" s="33" t="s">
+        <v>623</v>
+      </c>
+      <c r="C217" s="35" t="s">
+        <v>693</v>
+      </c>
+      <c r="D217" s="38">
+        <v>2021</v>
+      </c>
+      <c r="E217" s="28" t="s">
+        <v>651</v>
+      </c>
+      <c r="F217" s="34" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" ht="15" customHeight="1">
+      <c r="A218" s="33" t="s">
+        <v>650</v>
+      </c>
+      <c r="B218" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C218" s="35" t="s">
+        <v>694</v>
+      </c>
+      <c r="D218" s="38">
+        <v>2021</v>
+      </c>
+      <c r="E218" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F218" s="34" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" ht="15" customHeight="1">
+      <c r="A219" s="33" t="s">
+        <v>650</v>
+      </c>
+      <c r="B219" s="1" t="s">
+        <v>602</v>
+      </c>
+      <c r="C219" s="35" t="s">
+        <v>695</v>
+      </c>
+      <c r="D219" s="38">
+        <v>2021</v>
+      </c>
+      <c r="E219" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F219" s="34" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" ht="15" customHeight="1">
+      <c r="A220" s="33" t="s">
+        <v>649</v>
+      </c>
+      <c r="B220" s="33" t="s">
+        <v>602</v>
+      </c>
+      <c r="C220" s="35" t="s">
+        <v>696</v>
+      </c>
+      <c r="D220" s="38">
+        <v>2021</v>
+      </c>
+      <c r="E220" s="28" t="s">
+        <v>652</v>
+      </c>
+      <c r="F220" s="34" t="s">
+        <v>622</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
